--- a/paletten-optimierer/data/draht_mueller_palettenliste.xlsx
+++ b/paletten-optimierer/data/draht_mueller_palettenliste.xlsx
@@ -526,7 +526,7 @@
         <v>350</v>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>125</v>
       </c>
       <c r="G9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>112</v>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>125</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>500</v>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>500</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>112</v>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>1000</v>
       </c>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>2100</v>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>267</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>150</v>
       </c>
       <c r="G21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>112</v>
       </c>
       <c r="G23" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>112</v>
       </c>
       <c r="G24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>112</v>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>112</v>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>500</v>
       </c>
       <c r="G27" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>360</v>
       </c>
       <c r="G28" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>360</v>
       </c>
       <c r="G29" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>1000</v>
       </c>
       <c r="G30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>360</v>
       </c>
       <c r="G31" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>38</v>
       </c>
       <c r="G32" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>250</v>
       </c>
       <c r="G33" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>250</v>
       </c>
       <c r="G34" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>360</v>
       </c>
       <c r="G35" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>55</v>
       </c>
       <c r="G36" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>250</v>
       </c>
       <c r="G38" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>360</v>
       </c>
       <c r="G39" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>360</v>
       </c>
       <c r="G40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>360</v>
       </c>
       <c r="G41" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>360</v>
       </c>
       <c r="G42" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>250</v>
       </c>
       <c r="G43" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>1000</v>
       </c>
       <c r="G44" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>360</v>
       </c>
       <c r="G45" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>100</v>
       </c>
       <c r="G46" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>1500</v>
       </c>
       <c r="G47" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>66</v>
       </c>
       <c r="G48" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136</v>
       </c>
       <c r="G49" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>40</v>
       </c>
       <c r="G50" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>50</v>
       </c>
       <c r="G51" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>1000</v>
       </c>
       <c r="G52" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>100</v>
       </c>
       <c r="G53" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>1000</v>
       </c>
       <c r="G54" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>100</v>
       </c>
       <c r="G55" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>360</v>
       </c>
       <c r="G56" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>360</v>
       </c>
       <c r="G57" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>1000</v>
       </c>
       <c r="G58" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>1000</v>
       </c>
       <c r="G59" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>1000</v>
       </c>
       <c r="G60" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>250</v>
       </c>
       <c r="G61" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>250</v>
       </c>
       <c r="G62" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>1000</v>
       </c>
       <c r="G63" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>2500</v>
       </c>
       <c r="G64" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>1000</v>
       </c>
       <c r="G65" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>1500</v>
       </c>
       <c r="G66" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>250</v>
       </c>
       <c r="G67" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>750</v>
       </c>
       <c r="G68" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>500</v>
       </c>
       <c r="G69" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>360</v>
       </c>
       <c r="G70" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>1000</v>
       </c>
       <c r="G71" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>1000</v>
       </c>
       <c r="G72" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>200</v>
       </c>
       <c r="G73" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>100</v>
       </c>
       <c r="G74" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>100</v>
       </c>
       <c r="G75" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>100</v>
       </c>
       <c r="G76" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>1500</v>
       </c>
       <c r="G77" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>50</v>
       </c>
       <c r="G78" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>50</v>
       </c>
       <c r="G79" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>100</v>
       </c>
       <c r="G80" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>200</v>
       </c>
       <c r="G81" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>360</v>
       </c>
       <c r="G82" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>360</v>
       </c>
       <c r="G83" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>38</v>
       </c>
       <c r="G84" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>2100</v>
       </c>
       <c r="G85" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>650</v>
       </c>
       <c r="G86" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>1000</v>
       </c>
       <c r="G87" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>360</v>
       </c>
       <c r="G88" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>650</v>
       </c>
       <c r="G89" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>360</v>
       </c>
       <c r="G90" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>250</v>
       </c>
       <c r="G91" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         <v>125</v>
       </c>
       <c r="G92" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>1200</v>
       </c>
       <c r="G93" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>100</v>
       </c>
       <c r="G94" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>400</v>
       </c>
       <c r="G95" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>100</v>
       </c>
       <c r="G96" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>100</v>
       </c>
       <c r="G97" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>100</v>
       </c>
       <c r="G98" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>500</v>
       </c>
       <c r="G99" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>500</v>
       </c>
       <c r="G100" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>500</v>
       </c>
       <c r="G101" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>500</v>
       </c>
       <c r="G102" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>500</v>
       </c>
       <c r="G103" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>500</v>
       </c>
       <c r="G104" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>60</v>
       </c>
       <c r="G105" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>333</v>
       </c>
       <c r="G106" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>55</v>
       </c>
       <c r="G107" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>55</v>
       </c>
       <c r="G108" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>66</v>
       </c>
       <c r="G109" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>50</v>
       </c>
       <c r="G110" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>10</v>
       </c>
       <c r="G111" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>40</v>
       </c>
       <c r="G112" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>500</v>
       </c>
       <c r="G113" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>500</v>
       </c>
       <c r="G114" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>500</v>
       </c>
       <c r="G115" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>100</v>
       </c>
       <c r="G116" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>100</v>
       </c>
       <c r="G117" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>38</v>
       </c>
       <c r="G118" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>55</v>
       </c>
       <c r="G119" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>55</v>
       </c>
       <c r="G120" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>55</v>
       </c>
       <c r="G121" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>25</v>
       </c>
       <c r="G122" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>500</v>
       </c>
       <c r="G123" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>300</v>
       </c>
       <c r="G124" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>50</v>
       </c>
       <c r="G125" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>2000</v>
       </c>
       <c r="G126" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>2000</v>
       </c>
       <c r="G127" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>2000</v>
       </c>
       <c r="G128" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>100</v>
       </c>
       <c r="G129" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>650</v>
       </c>
       <c r="G130" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>360</v>
       </c>
       <c r="G131" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>25</v>
       </c>
       <c r="G132" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>172</v>
       </c>
       <c r="G133" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>750</v>
       </c>
       <c r="G134" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>50</v>
       </c>
       <c r="G135" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>300</v>
       </c>
       <c r="G136" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>400</v>
       </c>
       <c r="G137" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>350</v>
       </c>
       <c r="G138" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>50</v>
       </c>
       <c r="G139" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>50</v>
       </c>
       <c r="G140" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>100</v>
       </c>
       <c r="G141" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>100</v>
       </c>
       <c r="G142" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>360</v>
       </c>
       <c r="G143" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>300</v>
       </c>
       <c r="G144" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>400</v>
       </c>
       <c r="G145" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>55</v>
       </c>
       <c r="G146" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>55</v>
       </c>
       <c r="G147" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>112</v>
       </c>
       <c r="G148" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>200</v>
       </c>
       <c r="G149" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>55</v>
       </c>
       <c r="G150" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>55</v>
       </c>
       <c r="G151" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>55</v>
       </c>
       <c r="G152" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>50</v>
       </c>
       <c r="G153" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>50</v>
       </c>
       <c r="G154" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>100</v>
       </c>
       <c r="G155" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>100</v>
       </c>
       <c r="G156" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>50</v>
       </c>
       <c r="G157" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>112</v>
       </c>
       <c r="G158" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>66</v>
       </c>
       <c r="G159" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         <v>360</v>
       </c>
       <c r="G160" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>200</v>
       </c>
       <c r="G161" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>4200</v>
       </c>
       <c r="G162" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>250</v>
       </c>
       <c r="G163" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>150</v>
       </c>
       <c r="G164" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>150</v>
       </c>
       <c r="G165" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>150</v>
       </c>
       <c r="G166" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>150</v>
       </c>
       <c r="G167" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>360</v>
       </c>
       <c r="G168" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>360</v>
       </c>
       <c r="G169" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>360</v>
       </c>
       <c r="G170" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>150</v>
       </c>
       <c r="G171" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>72</v>
       </c>
       <c r="G172" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>150</v>
       </c>
       <c r="G173" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>250</v>
       </c>
       <c r="G174" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>250</v>
       </c>
       <c r="G175" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>360</v>
       </c>
       <c r="G176" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>400</v>
       </c>
       <c r="G177" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>172</v>
       </c>
       <c r="G178" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>400</v>
       </c>
       <c r="G179" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>50</v>
       </c>
       <c r="G180" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>50</v>
       </c>
       <c r="G181" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>50</v>
       </c>
       <c r="G182" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>50</v>
       </c>
       <c r="G183" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>150</v>
       </c>
       <c r="G184" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>100</v>
       </c>
       <c r="G185" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>360</v>
       </c>
       <c r="G186" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>360</v>
       </c>
       <c r="G187" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>1000</v>
       </c>
       <c r="G188" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>1000</v>
       </c>
       <c r="G189" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>1000</v>
       </c>
       <c r="G190" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>250</v>
       </c>
       <c r="G191" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>1000</v>
       </c>
       <c r="G192" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>250</v>
       </c>
       <c r="G193" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>250</v>
       </c>
       <c r="G194" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>250</v>
       </c>
       <c r="G195" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>250</v>
       </c>
       <c r="G196" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>55</v>
       </c>
       <c r="G197" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>55</v>
       </c>
       <c r="G198" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>55</v>
       </c>
       <c r="G199" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>55</v>
       </c>
       <c r="G200" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>150</v>
       </c>
       <c r="G201" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>250</v>
       </c>
       <c r="G202" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>100</v>
       </c>
       <c r="G203" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>360</v>
       </c>
       <c r="G204" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>360</v>
       </c>
       <c r="G205" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>250</v>
       </c>
       <c r="G206" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>400</v>
       </c>
       <c r="G207" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>300</v>
       </c>
       <c r="G208" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>100</v>
       </c>
       <c r="G209" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>250</v>
       </c>
       <c r="G210" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>50</v>
       </c>
       <c r="G211" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>800</v>
       </c>
       <c r="G212" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>50</v>
       </c>
       <c r="G213" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>50</v>
       </c>
       <c r="G214" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>50</v>
       </c>
       <c r="G215" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>150</v>
       </c>
       <c r="G216" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>250</v>
       </c>
       <c r="G217" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>250</v>
       </c>
       <c r="G218" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>100</v>
       </c>
       <c r="G219" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>400</v>
       </c>
       <c r="G220" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>250</v>
       </c>
       <c r="G221" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>250</v>
       </c>
       <c r="G222" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>250</v>
       </c>
       <c r="G223" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>250</v>
       </c>
       <c r="G224" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>360</v>
       </c>
       <c r="G225" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>360</v>
       </c>
       <c r="G226" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>360</v>
       </c>
       <c r="G227" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>360</v>
       </c>
       <c r="G228" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>750</v>
       </c>
       <c r="G229" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>100</v>
       </c>
       <c r="G230" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>100</v>
       </c>
       <c r="G231" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>100</v>
       </c>
       <c r="G232" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         <v>1250</v>
       </c>
       <c r="G233" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>750</v>
       </c>
       <c r="G234" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>3000</v>
       </c>
       <c r="G235" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>50</v>
       </c>
       <c r="G236" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>38</v>
       </c>
       <c r="G237" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>50</v>
       </c>
       <c r="G238" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>360</v>
       </c>
       <c r="G239" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>360</v>
       </c>
       <c r="G240" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>360</v>
       </c>
       <c r="G241" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>360</v>
       </c>
       <c r="G242" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>250</v>
       </c>
       <c r="G243" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>400</v>
       </c>
       <c r="G244" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>400</v>
       </c>
       <c r="G245" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>100</v>
       </c>
       <c r="G246" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>160</v>
       </c>
       <c r="G247" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>250</v>
       </c>
       <c r="G248" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>150</v>
       </c>
       <c r="G249" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>650</v>
       </c>
       <c r="G250" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>72</v>
       </c>
       <c r="G251" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>200</v>
       </c>
       <c r="G252" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>1000</v>
       </c>
       <c r="G253" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>500</v>
       </c>
       <c r="G254" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>500</v>
       </c>
       <c r="G255" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>500</v>
       </c>
       <c r="G256" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>360</v>
       </c>
       <c r="G257" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>230</v>
       </c>
       <c r="G258" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>50</v>
       </c>
       <c r="G259" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>400</v>
       </c>
       <c r="G260" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>1500</v>
       </c>
       <c r="G261" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>38</v>
       </c>
       <c r="G262" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>650</v>
       </c>
       <c r="G263" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>150</v>
       </c>
       <c r="G264" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>55</v>
       </c>
       <c r="G265" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>400</v>
       </c>
       <c r="G266" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>400</v>
       </c>
       <c r="G267" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>2200</v>
       </c>
       <c r="G268" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>750</v>
       </c>
       <c r="G269" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>200</v>
       </c>
       <c r="G270" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>55</v>
       </c>
       <c r="G271" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>55</v>
       </c>
       <c r="G272" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>350</v>
       </c>
       <c r="G273" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>500</v>
       </c>
       <c r="G274" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>400</v>
       </c>
       <c r="G275" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>600</v>
       </c>
       <c r="G276" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>1200</v>
       </c>
       <c r="G277" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>360</v>
       </c>
       <c r="G278" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>500</v>
       </c>
       <c r="G279" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>150</v>
       </c>
       <c r="G280" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>150</v>
       </c>
       <c r="G281" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>160</v>
       </c>
       <c r="G282" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>250</v>
       </c>
       <c r="G283" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>55</v>
       </c>
       <c r="G284" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>55</v>
       </c>
       <c r="G285" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>55</v>
       </c>
       <c r="G286" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>55</v>
       </c>
       <c r="G287" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>1000</v>
       </c>
       <c r="G288" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>400</v>
       </c>
       <c r="G289" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>55</v>
       </c>
       <c r="G290" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>1000</v>
       </c>
       <c r="G291" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -14446,7 +14446,7 @@
         <v>250</v>
       </c>
       <c r="G292" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>125</v>
       </c>
       <c r="G293" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>50</v>
       </c>
       <c r="G294" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>1200</v>
       </c>
       <c r="G295" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>500</v>
       </c>
       <c r="G296" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>2000</v>
       </c>
       <c r="G297" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>3000</v>
       </c>
       <c r="G298" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>1500</v>
       </c>
       <c r="G299" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>400</v>
       </c>
       <c r="G300" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>360</v>
       </c>
       <c r="G301" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>750</v>
       </c>
       <c r="G302" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>750</v>
       </c>
       <c r="G303" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>150</v>
       </c>
       <c r="G304" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>360</v>
       </c>
       <c r="G305" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H305" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>500</v>
       </c>
       <c r="G306" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>200</v>
       </c>
       <c r="G307" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H307" t="inlineStr">
         <is>

--- a/paletten-optimierer/data/draht_mueller_palettenliste.xlsx
+++ b/paletten-optimierer/data/draht_mueller_palettenliste.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L307"/>
+  <dimension ref="A1:K307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -439,7 +439,6 @@
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,7 +464,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Benoetigte_Paletten</t>
+          <t>Menge</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -494,11 +493,6 @@
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Menge</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>KW_Fertigung</t>
         </is>
@@ -520,7 +514,7 @@
         <v>1100</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>350</v>
@@ -543,10 +537,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -568,7 +559,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -591,10 +582,7 @@
           <t>2620</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -639,10 +627,7 @@
           <t>2620</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -664,7 +649,7 @@
         <v>790</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
@@ -687,10 +672,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>5</v>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -712,7 +694,7 @@
         <v>1300</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
         <v>38</v>
@@ -735,10 +717,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>48</v>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -783,10 +762,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -831,10 +807,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -856,7 +829,7 @@
         <v>950</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>125</v>
@@ -879,10 +852,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -904,7 +874,7 @@
         <v>1340</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
         <v>112</v>
@@ -927,10 +897,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>9</v>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -952,7 +919,7 @@
         <v>500</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
         <v>125</v>
@@ -975,10 +942,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1000,7 +964,7 @@
         <v>930</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>500</v>
@@ -1023,10 +987,7 @@
           <t>2634</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1048,7 +1009,7 @@
         <v>930</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>500</v>
@@ -1071,10 +1032,7 @@
           <t>2633</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1096,7 +1054,7 @@
         <v>1200</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
         <v>112</v>
@@ -1119,10 +1077,7 @@
           <t>2610</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1167,10 +1122,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1192,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>50</v>
@@ -1215,10 +1167,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1263,10 +1212,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1311,10 +1257,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1336,7 +1279,7 @@
         <v>1060</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
         <v>2100</v>
@@ -1359,10 +1302,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1384,7 +1324,7 @@
         <v>675</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
         <v>267</v>
@@ -1407,10 +1347,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1432,7 +1369,7 @@
         <v>985</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
         <v>150</v>
@@ -1455,10 +1392,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1480,7 +1414,7 @@
         <v>975</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F22" t="n">
         <v>30</v>
@@ -1503,10 +1437,7 @@
           <t>2540</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>33</v>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1528,7 +1459,7 @@
         <v>1200</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
         <v>112</v>
@@ -1551,10 +1482,7 @@
           <t>2610</t>
         </is>
       </c>
-      <c r="K23" t="n">
-        <v>10</v>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1576,7 +1504,7 @@
         <v>1200</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F24" t="n">
         <v>112</v>
@@ -1599,10 +1527,7 @@
           <t>2610</t>
         </is>
       </c>
-      <c r="K24" t="n">
-        <v>10</v>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1624,7 +1549,7 @@
         <v>1200</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
         <v>112</v>
@@ -1647,10 +1572,7 @@
           <t>2610</t>
         </is>
       </c>
-      <c r="K25" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1672,7 +1594,7 @@
         <v>1200</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
         <v>112</v>
@@ -1695,10 +1617,7 @@
           <t>2610</t>
         </is>
       </c>
-      <c r="K26" t="n">
-        <v>10</v>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1743,10 +1662,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1791,10 +1707,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1839,10 +1752,7 @@
           <t>2619</t>
         </is>
       </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1887,10 +1797,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1935,10 +1842,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -1960,7 +1864,7 @@
         <v>1270</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F32" t="n">
         <v>38</v>
@@ -1983,10 +1887,7 @@
           <t>2631</t>
         </is>
       </c>
-      <c r="K32" t="n">
-        <v>27</v>
-      </c>
-      <c r="L32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2008,7 +1909,7 @@
         <v>1650</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F33" t="n">
         <v>250</v>
@@ -2031,10 +1932,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K33" t="n">
-        <v>36</v>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2056,7 +1954,7 @@
         <v>1650</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F34" t="n">
         <v>250</v>
@@ -2079,10 +1977,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K34" t="n">
-        <v>36</v>
-      </c>
-      <c r="L34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2104,7 +1999,7 @@
         <v>1470</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F35" t="n">
         <v>360</v>
@@ -2127,10 +2022,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K35" t="n">
-        <v>7</v>
-      </c>
-      <c r="L35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2175,10 +2067,7 @@
           <t>2619</t>
         </is>
       </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2223,10 +2112,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2248,7 +2134,7 @@
         <v>1650</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F38" t="n">
         <v>250</v>
@@ -2271,10 +2157,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K38" t="n">
-        <v>36</v>
-      </c>
-      <c r="L38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2296,7 +2179,7 @@
         <v>1460</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F39" t="n">
         <v>360</v>
@@ -2319,10 +2202,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K39" t="n">
-        <v>8</v>
-      </c>
-      <c r="L39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2344,7 +2224,7 @@
         <v>1490</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F40" t="n">
         <v>360</v>
@@ -2367,10 +2247,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K40" t="n">
-        <v>4</v>
-      </c>
-      <c r="L40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2392,7 +2269,7 @@
         <v>1460</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
         <v>360</v>
@@ -2415,10 +2292,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K41" t="n">
-        <v>2</v>
-      </c>
-      <c r="L41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2440,7 +2314,7 @@
         <v>1460</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
         <v>360</v>
@@ -2463,10 +2337,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K42" t="n">
-        <v>2</v>
-      </c>
-      <c r="L42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2488,7 +2359,7 @@
         <v>900</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
         <v>250</v>
@@ -2511,10 +2382,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K43" t="n">
-        <v>4</v>
-      </c>
-      <c r="L43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2559,10 +2427,7 @@
           <t>2620</t>
         </is>
       </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2584,7 +2449,7 @@
         <v>1460</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
         <v>360</v>
@@ -2607,10 +2472,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K45" t="n">
-        <v>2</v>
-      </c>
-      <c r="L45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2655,10 +2517,7 @@
           <t>2620</t>
         </is>
       </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2703,10 +2562,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2728,7 +2584,7 @@
         <v>880</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F48" t="n">
         <v>66</v>
@@ -2751,10 +2607,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K48" t="n">
-        <v>9</v>
-      </c>
-      <c r="L48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2799,10 +2652,7 @@
           <t>2619</t>
         </is>
       </c>
-      <c r="K49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2824,7 +2674,7 @@
         <v>350</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50" t="n">
         <v>40</v>
@@ -2847,10 +2697,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K50" t="n">
-        <v>4</v>
-      </c>
-      <c r="L50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2872,7 +2719,7 @@
         <v>700</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="n">
         <v>50</v>
@@ -2895,10 +2742,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K51" t="n">
-        <v>2</v>
-      </c>
-      <c r="L51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2943,10 +2787,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K52" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -2991,10 +2832,7 @@
           <t>2618</t>
         </is>
       </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3039,10 +2877,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K54" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3064,7 +2899,7 @@
         <v>540</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>100</v>
@@ -3087,10 +2922,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K55" t="n">
-        <v>2</v>
-      </c>
-      <c r="L55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3112,7 +2944,7 @@
         <v>1470</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>360</v>
@@ -3135,10 +2967,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K56" t="n">
-        <v>4</v>
-      </c>
-      <c r="L56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3160,7 +2989,7 @@
         <v>1470</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
         <v>360</v>
@@ -3183,10 +3012,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K57" t="n">
-        <v>4</v>
-      </c>
-      <c r="L57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3231,10 +3057,7 @@
           <t>2620</t>
         </is>
       </c>
-      <c r="K58" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3279,10 +3102,7 @@
           <t>2620</t>
         </is>
       </c>
-      <c r="K59" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3327,10 +3147,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K60" t="n">
-        <v>1</v>
-      </c>
-      <c r="L60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3375,10 +3192,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K61" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3400,7 +3214,7 @@
         <v>900</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" t="n">
         <v>250</v>
@@ -3423,10 +3237,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K62" t="n">
-        <v>3</v>
-      </c>
-      <c r="L62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3471,10 +3282,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K63" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3519,10 +3327,7 @@
           <t>2620</t>
         </is>
       </c>
-      <c r="K64" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3544,7 +3349,7 @@
         <v>880</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F65" t="n">
         <v>1000</v>
@@ -3567,10 +3372,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K65" t="n">
-        <v>14</v>
-      </c>
-      <c r="L65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3615,10 +3417,7 @@
           <t>2620</t>
         </is>
       </c>
-      <c r="K66" t="n">
-        <v>1</v>
-      </c>
-      <c r="L66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3640,7 +3439,7 @@
         <v>1520</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F67" t="n">
         <v>250</v>
@@ -3663,10 +3462,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K67" t="n">
-        <v>11</v>
-      </c>
-      <c r="L67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3688,7 +3484,7 @@
         <v>1630</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F68" t="n">
         <v>750</v>
@@ -3711,10 +3507,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K68" t="n">
-        <v>15</v>
-      </c>
-      <c r="L68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3736,7 +3529,7 @@
         <v>1520</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F69" t="n">
         <v>500</v>
@@ -3759,10 +3552,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K69" t="n">
-        <v>10</v>
-      </c>
-      <c r="L69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3784,7 +3574,7 @@
         <v>1470</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
         <v>360</v>
@@ -3807,10 +3597,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3855,10 +3642,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K71" t="n">
-        <v>1</v>
-      </c>
-      <c r="L71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3903,10 +3687,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K72" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3928,7 +3709,7 @@
         <v>1200</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F73" t="n">
         <v>200</v>
@@ -3951,10 +3732,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K73" t="n">
-        <v>6</v>
-      </c>
-      <c r="L73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -3976,7 +3754,7 @@
         <v>780</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F74" t="n">
         <v>100</v>
@@ -3999,10 +3777,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K74" t="n">
-        <v>3</v>
-      </c>
-      <c r="L74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -4047,10 +3822,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K75" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -4095,10 +3867,7 @@
           <t>2619</t>
         </is>
       </c>
-      <c r="K76" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -4143,10 +3912,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -4168,7 +3934,7 @@
         <v>350</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
         <v>50</v>
@@ -4191,10 +3957,7 @@
           <t>2619</t>
         </is>
       </c>
-      <c r="K78" t="n">
-        <v>2</v>
-      </c>
-      <c r="L78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -4216,7 +3979,7 @@
         <v>860</v>
       </c>
       <c r="E79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F79" t="n">
         <v>50</v>
@@ -4239,10 +4002,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K79" t="n">
-        <v>4</v>
-      </c>
-      <c r="L79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -4264,7 +4024,7 @@
         <v>540</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" t="n">
         <v>100</v>
@@ -4287,10 +4047,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K80" t="n">
-        <v>2</v>
-      </c>
-      <c r="L80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -4335,10 +4092,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K81" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>2619</t>
         </is>
@@ -4383,10 +4137,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K82" t="n">
-        <v>1</v>
-      </c>
-      <c r="L82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -4431,10 +4182,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K83" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -4456,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F84" t="n">
         <v>38</v>
@@ -4479,10 +4227,7 @@
           <t>2608</t>
         </is>
       </c>
-      <c r="K84" t="n">
-        <v>13</v>
-      </c>
-      <c r="L84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -4504,7 +4249,7 @@
         <v>1060</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
         <v>2100</v>
@@ -4527,10 +4272,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K85" t="n">
-        <v>3</v>
-      </c>
-      <c r="L85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -4552,7 +4294,7 @@
         <v>1040</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
         <v>650</v>
@@ -4575,10 +4317,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K86" t="n">
-        <v>3</v>
-      </c>
-      <c r="L86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -4623,10 +4362,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K87" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -4671,10 +4407,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K88" t="n">
-        <v>1</v>
-      </c>
-      <c r="L88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -4696,7 +4429,7 @@
         <v>1040</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F89" t="n">
         <v>650</v>
@@ -4719,10 +4452,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K89" t="n">
-        <v>3</v>
-      </c>
-      <c r="L89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -4767,10 +4497,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K90" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -4792,7 +4519,7 @@
         <v>1520</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F91" t="n">
         <v>250</v>
@@ -4815,10 +4542,7 @@
           <t>2617</t>
         </is>
       </c>
-      <c r="K91" t="n">
-        <v>28</v>
-      </c>
-      <c r="L91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -4840,7 +4564,7 @@
         <v>590</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
         <v>125</v>
@@ -4863,10 +4587,7 @@
           <t>2620</t>
         </is>
       </c>
-      <c r="K92" t="n">
-        <v>2</v>
-      </c>
-      <c r="L92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -4888,7 +4609,7 @@
         <v>1040</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
         <v>1200</v>
@@ -4911,10 +4632,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K93" t="n">
-        <v>2</v>
-      </c>
-      <c r="L93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -4959,10 +4677,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K94" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5007,10 +4722,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K95" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5032,7 +4744,7 @@
         <v>790</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" t="n">
         <v>100</v>
@@ -5055,10 +4767,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K96" t="n">
-        <v>2</v>
-      </c>
-      <c r="L96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5080,7 +4789,7 @@
         <v>780</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F97" t="n">
         <v>100</v>
@@ -5103,10 +4812,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K97" t="n">
-        <v>3</v>
-      </c>
-      <c r="L97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5128,7 +4834,7 @@
         <v>790</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" t="n">
         <v>100</v>
@@ -5151,10 +4857,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K98" t="n">
-        <v>2</v>
-      </c>
-      <c r="L98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5176,7 +4879,7 @@
         <v>960</v>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F99" t="n">
         <v>500</v>
@@ -5199,10 +4902,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K99" t="n">
-        <v>4</v>
-      </c>
-      <c r="L99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5247,10 +4947,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K100" t="n">
-        <v>1</v>
-      </c>
-      <c r="L100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5295,10 +4992,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K101" t="n">
-        <v>1</v>
-      </c>
-      <c r="L101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5320,7 +5014,7 @@
         <v>960</v>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" t="n">
         <v>500</v>
@@ -5343,10 +5037,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K102" t="n">
-        <v>2</v>
-      </c>
-      <c r="L102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5368,7 +5059,7 @@
         <v>960</v>
       </c>
       <c r="E103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" t="n">
         <v>500</v>
@@ -5391,10 +5082,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K103" t="n">
-        <v>2</v>
-      </c>
-      <c r="L103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5439,10 +5127,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K104" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5487,10 +5172,7 @@
           <t>2620</t>
         </is>
       </c>
-      <c r="K105" t="n">
-        <v>1</v>
-      </c>
-      <c r="L105" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5535,10 +5217,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K106" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5583,10 +5262,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K107" t="n">
-        <v>1</v>
-      </c>
-      <c r="L107" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5631,10 +5307,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K108" t="n">
-        <v>1</v>
-      </c>
-      <c r="L108" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5656,7 +5329,7 @@
         <v>880</v>
       </c>
       <c r="E109" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F109" t="n">
         <v>66</v>
@@ -5679,10 +5352,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K109" t="n">
-        <v>9</v>
-      </c>
-      <c r="L109" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5727,10 +5397,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K110" t="n">
-        <v>1</v>
-      </c>
-      <c r="L110" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5775,10 +5442,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K111" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5823,10 +5487,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K112" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5848,7 +5509,7 @@
         <v>960</v>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" t="n">
         <v>500</v>
@@ -5871,10 +5532,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K113" t="n">
-        <v>2</v>
-      </c>
-      <c r="L113" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5919,10 +5577,7 @@
           <t>2629</t>
         </is>
       </c>
-      <c r="K114" t="n">
-        <v>1</v>
-      </c>
-      <c r="L114" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -5967,10 +5622,7 @@
           <t>2631</t>
         </is>
       </c>
-      <c r="K115" t="n">
-        <v>1</v>
-      </c>
-      <c r="L115" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -6015,10 +5667,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K116" t="n">
-        <v>1</v>
-      </c>
-      <c r="L116" t="inlineStr">
+      <c r="K116" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -6063,10 +5712,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K117" t="n">
-        <v>1</v>
-      </c>
-      <c r="L117" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -6088,7 +5734,7 @@
         <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F118" t="n">
         <v>38</v>
@@ -6111,10 +5757,7 @@
           <t>2616</t>
         </is>
       </c>
-      <c r="K118" t="n">
-        <v>10</v>
-      </c>
-      <c r="L118" t="inlineStr">
+      <c r="K118" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -6159,10 +5802,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K119" t="n">
-        <v>1</v>
-      </c>
-      <c r="L119" t="inlineStr">
+      <c r="K119" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -6184,7 +5824,7 @@
         <v>1670</v>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F120" t="n">
         <v>55</v>
@@ -6207,10 +5847,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K120" t="n">
-        <v>4</v>
-      </c>
-      <c r="L120" t="inlineStr">
+      <c r="K120" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -6255,10 +5892,7 @@
           <t>2621</t>
         </is>
       </c>
-      <c r="K121" t="n">
-        <v>1</v>
-      </c>
-      <c r="L121" t="inlineStr">
+      <c r="K121" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -6303,10 +5937,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K122" t="n">
-        <v>1</v>
-      </c>
-      <c r="L122" t="inlineStr">
+      <c r="K122" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -6328,7 +5959,7 @@
         <v>1100</v>
       </c>
       <c r="E123" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F123" t="n">
         <v>500</v>
@@ -6351,10 +5982,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K123" t="n">
-        <v>4</v>
-      </c>
-      <c r="L123" t="inlineStr">
+      <c r="K123" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -6376,7 +6004,7 @@
         <v>570</v>
       </c>
       <c r="E124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" t="n">
         <v>300</v>
@@ -6399,10 +6027,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K124" t="n">
-        <v>2</v>
-      </c>
-      <c r="L124" t="inlineStr">
+      <c r="K124" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
@@ -6424,7 +6049,7 @@
         <v>280</v>
       </c>
       <c r="E125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" t="n">
         <v>50</v>
@@ -6447,10 +6072,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K125" t="n">
-        <v>2</v>
-      </c>
-      <c r="L125" t="inlineStr">
+      <c r="K125" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -6495,10 +6117,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K126" t="n">
-        <v>1</v>
-      </c>
-      <c r="L126" t="inlineStr">
+      <c r="K126" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -6520,7 +6139,7 @@
         <v>1210</v>
       </c>
       <c r="E127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" t="n">
         <v>2000</v>
@@ -6543,10 +6162,7 @@
           <t>2629</t>
         </is>
       </c>
-      <c r="K127" t="n">
-        <v>2</v>
-      </c>
-      <c r="L127" t="inlineStr">
+      <c r="K127" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -6568,7 +6184,7 @@
         <v>1210</v>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" t="n">
         <v>2000</v>
@@ -6591,10 +6207,7 @@
           <t>2635</t>
         </is>
       </c>
-      <c r="K128" t="n">
-        <v>2</v>
-      </c>
-      <c r="L128" t="inlineStr">
+      <c r="K128" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -6616,7 +6229,7 @@
         <v>790</v>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F129" t="n">
         <v>100</v>
@@ -6639,10 +6252,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K129" t="n">
-        <v>3</v>
-      </c>
-      <c r="L129" t="inlineStr">
+      <c r="K129" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -6664,7 +6274,7 @@
         <v>1040</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F130" t="n">
         <v>650</v>
@@ -6687,10 +6297,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K130" t="n">
-        <v>3</v>
-      </c>
-      <c r="L130" t="inlineStr">
+      <c r="K130" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -6735,10 +6342,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K131" t="n">
-        <v>1</v>
-      </c>
-      <c r="L131" t="inlineStr">
+      <c r="K131" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -6760,7 +6364,7 @@
         <v>400</v>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F132" t="n">
         <v>25</v>
@@ -6783,10 +6387,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K132" t="n">
-        <v>4</v>
-      </c>
-      <c r="L132" t="inlineStr">
+      <c r="K132" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -6808,7 +6409,7 @@
         <v>1050</v>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F133" t="n">
         <v>172</v>
@@ -6831,10 +6432,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K133" t="n">
-        <v>4</v>
-      </c>
-      <c r="L133" t="inlineStr">
+      <c r="K133" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -6879,10 +6477,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K134" t="n">
-        <v>1</v>
-      </c>
-      <c r="L134" t="inlineStr">
+      <c r="K134" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -6927,10 +6522,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K135" t="n">
-        <v>1</v>
-      </c>
-      <c r="L135" t="inlineStr">
+      <c r="K135" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -6952,7 +6544,7 @@
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F136" t="n">
         <v>300</v>
@@ -6975,10 +6567,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K136" t="n">
-        <v>4</v>
-      </c>
-      <c r="L136" t="inlineStr">
+      <c r="K136" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7000,7 +6589,7 @@
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F137" t="n">
         <v>400</v>
@@ -7023,10 +6612,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K137" t="n">
-        <v>3</v>
-      </c>
-      <c r="L137" t="inlineStr">
+      <c r="K137" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7048,7 +6634,7 @@
         <v>1045</v>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F138" t="n">
         <v>350</v>
@@ -7071,10 +6657,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K138" t="n">
-        <v>3</v>
-      </c>
-      <c r="L138" t="inlineStr">
+      <c r="K138" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7096,7 +6679,7 @@
         <v>400</v>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" t="n">
         <v>50</v>
@@ -7119,10 +6702,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K139" t="n">
-        <v>2</v>
-      </c>
-      <c r="L139" t="inlineStr">
+      <c r="K139" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7144,7 +6724,7 @@
         <v>400</v>
       </c>
       <c r="E140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F140" t="n">
         <v>50</v>
@@ -7167,10 +6747,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K140" t="n">
-        <v>2</v>
-      </c>
-      <c r="L140" t="inlineStr">
+      <c r="K140" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7192,7 +6769,7 @@
         <v>400</v>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F141" t="n">
         <v>100</v>
@@ -7215,10 +6792,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K141" t="n">
-        <v>4</v>
-      </c>
-      <c r="L141" t="inlineStr">
+      <c r="K141" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7263,10 +6837,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K142" t="n">
-        <v>1</v>
-      </c>
-      <c r="L142" t="inlineStr">
+      <c r="K142" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7288,7 +6859,7 @@
         <v>1470</v>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F143" t="n">
         <v>360</v>
@@ -7311,10 +6882,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K143" t="n">
-        <v>4</v>
-      </c>
-      <c r="L143" t="inlineStr">
+      <c r="K143" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7336,7 +6904,7 @@
         <v>670</v>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F144" t="n">
         <v>300</v>
@@ -7359,10 +6927,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K144" t="n">
-        <v>3</v>
-      </c>
-      <c r="L144" t="inlineStr">
+      <c r="K144" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7407,10 +6972,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K145" t="n">
-        <v>1</v>
-      </c>
-      <c r="L145" t="inlineStr">
+      <c r="K145" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7455,10 +7017,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K146" t="n">
-        <v>1</v>
-      </c>
-      <c r="L146" t="inlineStr">
+      <c r="K146" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7480,7 +7039,7 @@
         <v>1670</v>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F147" t="n">
         <v>55</v>
@@ -7503,10 +7062,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K147" t="n">
-        <v>3</v>
-      </c>
-      <c r="L147" t="inlineStr">
+      <c r="K147" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7528,7 +7084,7 @@
         <v>1340</v>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F148" t="n">
         <v>112</v>
@@ -7551,10 +7107,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K148" t="n">
-        <v>11</v>
-      </c>
-      <c r="L148" t="inlineStr">
+      <c r="K148" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7576,7 +7129,7 @@
         <v>1200</v>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F149" t="n">
         <v>200</v>
@@ -7599,10 +7152,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K149" t="n">
-        <v>4</v>
-      </c>
-      <c r="L149" t="inlineStr">
+      <c r="K149" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7624,7 +7174,7 @@
         <v>1690</v>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F150" t="n">
         <v>55</v>
@@ -7647,10 +7197,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K150" t="n">
-        <v>8</v>
-      </c>
-      <c r="L150" t="inlineStr">
+      <c r="K150" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7672,7 +7219,7 @@
         <v>1690</v>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F151" t="n">
         <v>55</v>
@@ -7695,10 +7242,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K151" t="n">
-        <v>4</v>
-      </c>
-      <c r="L151" t="inlineStr">
+      <c r="K151" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7720,7 +7264,7 @@
         <v>1170</v>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F152" t="n">
         <v>55</v>
@@ -7743,10 +7287,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K152" t="n">
-        <v>8</v>
-      </c>
-      <c r="L152" t="inlineStr">
+      <c r="K152" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7791,10 +7332,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K153" t="n">
-        <v>1</v>
-      </c>
-      <c r="L153" t="inlineStr">
+      <c r="K153" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7839,10 +7377,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K154" t="n">
-        <v>1</v>
-      </c>
-      <c r="L154" t="inlineStr">
+      <c r="K154" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7864,7 +7399,7 @@
         <v>400</v>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F155" t="n">
         <v>100</v>
@@ -7887,10 +7422,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K155" t="n">
-        <v>5</v>
-      </c>
-      <c r="L155" t="inlineStr">
+      <c r="K155" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7912,7 +7444,7 @@
         <v>360</v>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F156" t="n">
         <v>100</v>
@@ -7935,10 +7467,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K156" t="n">
-        <v>3</v>
-      </c>
-      <c r="L156" t="inlineStr">
+      <c r="K156" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -7983,10 +7512,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K157" t="n">
-        <v>1</v>
-      </c>
-      <c r="L157" t="inlineStr">
+      <c r="K157" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -8008,7 +7534,7 @@
         <v>1340</v>
       </c>
       <c r="E158" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F158" t="n">
         <v>112</v>
@@ -8031,10 +7557,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K158" t="n">
-        <v>18</v>
-      </c>
-      <c r="L158" t="inlineStr">
+      <c r="K158" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -8056,7 +7579,7 @@
         <v>880</v>
       </c>
       <c r="E159" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F159" t="n">
         <v>66</v>
@@ -8079,10 +7602,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K159" t="n">
-        <v>8</v>
-      </c>
-      <c r="L159" t="inlineStr">
+      <c r="K159" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -8127,10 +7647,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K160" t="n">
-        <v>1</v>
-      </c>
-      <c r="L160" t="inlineStr">
+      <c r="K160" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -8175,10 +7692,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K161" t="n">
-        <v>1</v>
-      </c>
-      <c r="L161" t="inlineStr">
+      <c r="K161" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -8223,10 +7737,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K162" t="n">
-        <v>1</v>
-      </c>
-      <c r="L162" t="inlineStr">
+      <c r="K162" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
@@ -8248,7 +7759,7 @@
         <v>1250</v>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F163" t="n">
         <v>250</v>
@@ -8271,10 +7782,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K163" t="n">
-        <v>3</v>
-      </c>
-      <c r="L163" t="inlineStr">
+      <c r="K163" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8296,7 +7804,7 @@
         <v>1130</v>
       </c>
       <c r="E164" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F164" t="n">
         <v>150</v>
@@ -8319,10 +7827,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K164" t="n">
-        <v>7</v>
-      </c>
-      <c r="L164" t="inlineStr">
+      <c r="K164" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8344,7 +7849,7 @@
         <v>1130</v>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F165" t="n">
         <v>150</v>
@@ -8367,10 +7872,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K165" t="n">
-        <v>7</v>
-      </c>
-      <c r="L165" t="inlineStr">
+      <c r="K165" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8392,7 +7894,7 @@
         <v>1130</v>
       </c>
       <c r="E166" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F166" t="n">
         <v>150</v>
@@ -8415,10 +7917,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K166" t="n">
-        <v>7</v>
-      </c>
-      <c r="L166" t="inlineStr">
+      <c r="K166" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8440,7 +7939,7 @@
         <v>1130</v>
       </c>
       <c r="E167" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F167" t="n">
         <v>150</v>
@@ -8463,10 +7962,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K167" t="n">
-        <v>7</v>
-      </c>
-      <c r="L167" t="inlineStr">
+      <c r="K167" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8511,10 +8007,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K168" t="n">
-        <v>1</v>
-      </c>
-      <c r="L168" t="inlineStr">
+      <c r="K168" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8559,10 +8052,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K169" t="n">
-        <v>1</v>
-      </c>
-      <c r="L169" t="inlineStr">
+      <c r="K169" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8607,10 +8097,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K170" t="n">
-        <v>1</v>
-      </c>
-      <c r="L170" t="inlineStr">
+      <c r="K170" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8632,7 +8119,7 @@
         <v>1210</v>
       </c>
       <c r="E171" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F171" t="n">
         <v>150</v>
@@ -8655,10 +8142,7 @@
           <t>2622</t>
         </is>
       </c>
-      <c r="K171" t="n">
-        <v>13</v>
-      </c>
-      <c r="L171" t="inlineStr">
+      <c r="K171" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8680,7 +8164,7 @@
         <v>1380</v>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F172" t="n">
         <v>72</v>
@@ -8703,10 +8187,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K172" t="n">
-        <v>25</v>
-      </c>
-      <c r="L172" t="inlineStr">
+      <c r="K172" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8728,7 +8209,7 @@
         <v>1200</v>
       </c>
       <c r="E173" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F173" t="n">
         <v>150</v>
@@ -8751,10 +8232,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K173" t="n">
-        <v>13</v>
-      </c>
-      <c r="L173" t="inlineStr">
+      <c r="K173" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8776,7 +8254,7 @@
         <v>900</v>
       </c>
       <c r="E174" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F174" t="n">
         <v>250</v>
@@ -8799,10 +8277,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K174" t="n">
-        <v>8</v>
-      </c>
-      <c r="L174" t="inlineStr">
+      <c r="K174" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8824,7 +8299,7 @@
         <v>900</v>
       </c>
       <c r="E175" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F175" t="n">
         <v>250</v>
@@ -8847,10 +8322,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K175" t="n">
-        <v>3</v>
-      </c>
-      <c r="L175" t="inlineStr">
+      <c r="K175" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8872,7 +8344,7 @@
         <v>1460</v>
       </c>
       <c r="E176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F176" t="n">
         <v>360</v>
@@ -8895,10 +8367,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K176" t="n">
-        <v>2</v>
-      </c>
-      <c r="L176" t="inlineStr">
+      <c r="K176" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8920,7 +8389,7 @@
         <v>1360</v>
       </c>
       <c r="E177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F177" t="n">
         <v>400</v>
@@ -8943,10 +8412,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K177" t="n">
-        <v>2</v>
-      </c>
-      <c r="L177" t="inlineStr">
+      <c r="K177" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -8968,7 +8434,7 @@
         <v>1080</v>
       </c>
       <c r="E178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F178" t="n">
         <v>172</v>
@@ -8991,10 +8457,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K178" t="n">
-        <v>3</v>
-      </c>
-      <c r="L178" t="inlineStr">
+      <c r="K178" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9039,10 +8502,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K179" t="n">
-        <v>1</v>
-      </c>
-      <c r="L179" t="inlineStr">
+      <c r="K179" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9064,7 +8524,7 @@
         <v>400</v>
       </c>
       <c r="E180" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F180" t="n">
         <v>50</v>
@@ -9087,10 +8547,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K180" t="n">
-        <v>16</v>
-      </c>
-      <c r="L180" t="inlineStr">
+      <c r="K180" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9112,7 +8569,7 @@
         <v>400</v>
       </c>
       <c r="E181" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F181" t="n">
         <v>50</v>
@@ -9135,10 +8592,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K181" t="n">
-        <v>4</v>
-      </c>
-      <c r="L181" t="inlineStr">
+      <c r="K181" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9160,7 +8614,7 @@
         <v>400</v>
       </c>
       <c r="E182" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F182" t="n">
         <v>50</v>
@@ -9183,10 +8637,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K182" t="n">
-        <v>8</v>
-      </c>
-      <c r="L182" t="inlineStr">
+      <c r="K182" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9208,7 +8659,7 @@
         <v>400</v>
       </c>
       <c r="E183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F183" t="n">
         <v>50</v>
@@ -9231,10 +8682,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K183" t="n">
-        <v>2</v>
-      </c>
-      <c r="L183" t="inlineStr">
+      <c r="K183" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9256,7 +8704,7 @@
         <v>745</v>
       </c>
       <c r="E184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F184" t="n">
         <v>150</v>
@@ -9279,10 +8727,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K184" t="n">
-        <v>2</v>
-      </c>
-      <c r="L184" t="inlineStr">
+      <c r="K184" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9304,7 +8749,7 @@
         <v>750</v>
       </c>
       <c r="E185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F185" t="n">
         <v>100</v>
@@ -9327,10 +8772,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K185" t="n">
-        <v>3</v>
-      </c>
-      <c r="L185" t="inlineStr">
+      <c r="K185" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9352,7 +8794,7 @@
         <v>1470</v>
       </c>
       <c r="E186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F186" t="n">
         <v>360</v>
@@ -9375,10 +8817,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K186" t="n">
-        <v>2</v>
-      </c>
-      <c r="L186" t="inlineStr">
+      <c r="K186" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9400,7 +8839,7 @@
         <v>1470</v>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F187" t="n">
         <v>360</v>
@@ -9423,10 +8862,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K187" t="n">
-        <v>2</v>
-      </c>
-      <c r="L187" t="inlineStr">
+      <c r="K187" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9448,7 +8884,7 @@
         <v>800</v>
       </c>
       <c r="E188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F188" t="n">
         <v>1000</v>
@@ -9471,10 +8907,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K188" t="n">
-        <v>3</v>
-      </c>
-      <c r="L188" t="inlineStr">
+      <c r="K188" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9496,7 +8929,7 @@
         <v>1220</v>
       </c>
       <c r="E189" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F189" t="n">
         <v>1000</v>
@@ -9519,10 +8952,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K189" t="n">
-        <v>3</v>
-      </c>
-      <c r="L189" t="inlineStr">
+      <c r="K189" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9567,10 +8997,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K190" t="n">
-        <v>1</v>
-      </c>
-      <c r="L190" t="inlineStr">
+      <c r="K190" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9592,7 +9019,7 @@
         <v>900</v>
       </c>
       <c r="E191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F191" t="n">
         <v>250</v>
@@ -9615,10 +9042,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K191" t="n">
-        <v>3</v>
-      </c>
-      <c r="L191" t="inlineStr">
+      <c r="K191" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9663,10 +9087,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K192" t="n">
-        <v>1</v>
-      </c>
-      <c r="L192" t="inlineStr">
+      <c r="K192" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9688,7 +9109,7 @@
         <v>900</v>
       </c>
       <c r="E193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F193" t="n">
         <v>250</v>
@@ -9711,10 +9132,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K193" t="n">
-        <v>2</v>
-      </c>
-      <c r="L193" t="inlineStr">
+      <c r="K193" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9736,7 +9154,7 @@
         <v>900</v>
       </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F194" t="n">
         <v>250</v>
@@ -9759,10 +9177,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K194" t="n">
-        <v>2</v>
-      </c>
-      <c r="L194" t="inlineStr">
+      <c r="K194" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9784,7 +9199,7 @@
         <v>900</v>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F195" t="n">
         <v>250</v>
@@ -9807,10 +9222,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K195" t="n">
-        <v>2</v>
-      </c>
-      <c r="L195" t="inlineStr">
+      <c r="K195" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9832,7 +9244,7 @@
         <v>900</v>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F196" t="n">
         <v>250</v>
@@ -9855,10 +9267,7 @@
           <t>2628</t>
         </is>
       </c>
-      <c r="K196" t="n">
-        <v>2</v>
-      </c>
-      <c r="L196" t="inlineStr">
+      <c r="K196" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9903,10 +9312,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K197" t="n">
-        <v>1</v>
-      </c>
-      <c r="L197" t="inlineStr">
+      <c r="K197" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9951,10 +9357,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K198" t="n">
-        <v>1</v>
-      </c>
-      <c r="L198" t="inlineStr">
+      <c r="K198" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -9976,7 +9379,7 @@
         <v>1170</v>
       </c>
       <c r="E199" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F199" t="n">
         <v>55</v>
@@ -9999,10 +9402,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K199" t="n">
-        <v>3</v>
-      </c>
-      <c r="L199" t="inlineStr">
+      <c r="K199" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -10047,10 +9447,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K200" t="n">
-        <v>1</v>
-      </c>
-      <c r="L200" t="inlineStr">
+      <c r="K200" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -10072,7 +9469,7 @@
         <v>1200</v>
       </c>
       <c r="E201" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F201" t="n">
         <v>150</v>
@@ -10095,10 +9492,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K201" t="n">
-        <v>13</v>
-      </c>
-      <c r="L201" t="inlineStr">
+      <c r="K201" t="inlineStr">
         <is>
           <t>2622</t>
         </is>
@@ -10120,7 +9514,7 @@
         <v>1650</v>
       </c>
       <c r="E202" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F202" t="n">
         <v>250</v>
@@ -10143,10 +9537,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K202" t="n">
-        <v>36</v>
-      </c>
-      <c r="L202" t="inlineStr">
+      <c r="K202" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10191,10 +9582,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K203" t="n">
-        <v>1</v>
-      </c>
-      <c r="L203" t="inlineStr">
+      <c r="K203" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10239,10 +9627,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K204" t="n">
-        <v>1</v>
-      </c>
-      <c r="L204" t="inlineStr">
+      <c r="K204" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10287,10 +9672,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K205" t="n">
-        <v>1</v>
-      </c>
-      <c r="L205" t="inlineStr">
+      <c r="K205" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10312,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="E206" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F206" t="n">
         <v>250</v>
@@ -10335,10 +9717,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K206" t="n">
-        <v>5</v>
-      </c>
-      <c r="L206" t="inlineStr">
+      <c r="K206" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10360,7 +9739,7 @@
         <v>1330</v>
       </c>
       <c r="E207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F207" t="n">
         <v>400</v>
@@ -10383,10 +9762,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K207" t="n">
-        <v>3</v>
-      </c>
-      <c r="L207" t="inlineStr">
+      <c r="K207" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10431,10 +9807,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K208" t="n">
-        <v>1</v>
-      </c>
-      <c r="L208" t="inlineStr">
+      <c r="K208" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10479,10 +9852,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K209" t="n">
-        <v>1</v>
-      </c>
-      <c r="L209" t="inlineStr">
+      <c r="K209" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10527,10 +9897,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K210" t="n">
-        <v>1</v>
-      </c>
-      <c r="L210" t="inlineStr">
+      <c r="K210" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10552,7 +9919,7 @@
         <v>780</v>
       </c>
       <c r="E211" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F211" t="n">
         <v>50</v>
@@ -10575,10 +9942,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K211" t="n">
-        <v>4</v>
-      </c>
-      <c r="L211" t="inlineStr">
+      <c r="K211" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10623,10 +9987,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K212" t="n">
-        <v>1</v>
-      </c>
-      <c r="L212" t="inlineStr">
+      <c r="K212" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10671,10 +10032,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K213" t="n">
-        <v>1</v>
-      </c>
-      <c r="L213" t="inlineStr">
+      <c r="K213" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10696,7 +10054,7 @@
         <v>780</v>
       </c>
       <c r="E214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F214" t="n">
         <v>50</v>
@@ -10719,10 +10077,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K214" t="n">
-        <v>2</v>
-      </c>
-      <c r="L214" t="inlineStr">
+      <c r="K214" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10744,7 +10099,7 @@
         <v>780</v>
       </c>
       <c r="E215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F215" t="n">
         <v>50</v>
@@ -10767,10 +10122,7 @@
           <t>2628</t>
         </is>
       </c>
-      <c r="K215" t="n">
-        <v>2</v>
-      </c>
-      <c r="L215" t="inlineStr">
+      <c r="K215" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10815,10 +10167,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K216" t="n">
-        <v>1</v>
-      </c>
-      <c r="L216" t="inlineStr">
+      <c r="K216" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10863,10 +10212,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K217" t="n">
-        <v>1</v>
-      </c>
-      <c r="L217" t="inlineStr">
+      <c r="K217" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10911,10 +10257,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K218" t="n">
-        <v>1</v>
-      </c>
-      <c r="L218" t="inlineStr">
+      <c r="K218" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10936,7 +10279,7 @@
         <v>790</v>
       </c>
       <c r="E219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F219" t="n">
         <v>100</v>
@@ -10959,10 +10302,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K219" t="n">
-        <v>2</v>
-      </c>
-      <c r="L219" t="inlineStr">
+      <c r="K219" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -10984,7 +10324,7 @@
         <v>1360</v>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F220" t="n">
         <v>400</v>
@@ -11007,10 +10347,7 @@
           <t>2623</t>
         </is>
       </c>
-      <c r="K220" t="n">
-        <v>2</v>
-      </c>
-      <c r="L220" t="inlineStr">
+      <c r="K220" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11032,7 +10369,7 @@
         <v>1050</v>
       </c>
       <c r="E221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F221" t="n">
         <v>250</v>
@@ -11055,10 +10392,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K221" t="n">
-        <v>2</v>
-      </c>
-      <c r="L221" t="inlineStr">
+      <c r="K221" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11080,7 +10414,7 @@
         <v>870</v>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F222" t="n">
         <v>250</v>
@@ -11103,10 +10437,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K222" t="n">
-        <v>2</v>
-      </c>
-      <c r="L222" t="inlineStr">
+      <c r="K222" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11151,10 +10482,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K223" t="n">
-        <v>1</v>
-      </c>
-      <c r="L223" t="inlineStr">
+      <c r="K223" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11199,10 +10527,7 @@
           <t>2628</t>
         </is>
       </c>
-      <c r="K224" t="n">
-        <v>1</v>
-      </c>
-      <c r="L224" t="inlineStr">
+      <c r="K224" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11247,10 +10572,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K225" t="n">
-        <v>1</v>
-      </c>
-      <c r="L225" t="inlineStr">
+      <c r="K225" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11295,10 +10617,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K226" t="n">
-        <v>1</v>
-      </c>
-      <c r="L226" t="inlineStr">
+      <c r="K226" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11320,7 +10639,7 @@
         <v>1460</v>
       </c>
       <c r="E227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F227" t="n">
         <v>360</v>
@@ -11343,10 +10662,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K227" t="n">
-        <v>2</v>
-      </c>
-      <c r="L227" t="inlineStr">
+      <c r="K227" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11368,7 +10684,7 @@
         <v>1460</v>
       </c>
       <c r="E228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F228" t="n">
         <v>360</v>
@@ -11391,10 +10707,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K228" t="n">
-        <v>2</v>
-      </c>
-      <c r="L228" t="inlineStr">
+      <c r="K228" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11439,10 +10752,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K229" t="n">
-        <v>1</v>
-      </c>
-      <c r="L229" t="inlineStr">
+      <c r="K229" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11487,10 +10797,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K230" t="n">
-        <v>1</v>
-      </c>
-      <c r="L230" t="inlineStr">
+      <c r="K230" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11512,7 +10819,7 @@
         <v>400</v>
       </c>
       <c r="E231" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F231" t="n">
         <v>100</v>
@@ -11535,10 +10842,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K231" t="n">
-        <v>3</v>
-      </c>
-      <c r="L231" t="inlineStr">
+      <c r="K231" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11583,10 +10887,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K232" t="n">
-        <v>1</v>
-      </c>
-      <c r="L232" t="inlineStr">
+      <c r="K232" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11631,10 +10932,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K233" t="n">
-        <v>1</v>
-      </c>
-      <c r="L233" t="inlineStr">
+      <c r="K233" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11679,10 +10977,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K234" t="n">
-        <v>1</v>
-      </c>
-      <c r="L234" t="inlineStr">
+      <c r="K234" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11727,10 +11022,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K235" t="n">
-        <v>1</v>
-      </c>
-      <c r="L235" t="inlineStr">
+      <c r="K235" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11775,10 +11067,7 @@
           <t>2628</t>
         </is>
       </c>
-      <c r="K236" t="n">
-        <v>1</v>
-      </c>
-      <c r="L236" t="inlineStr">
+      <c r="K236" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11800,7 +11089,7 @@
         <v>1030</v>
       </c>
       <c r="E237" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F237" t="n">
         <v>38</v>
@@ -11823,10 +11112,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K237" t="n">
-        <v>3</v>
-      </c>
-      <c r="L237" t="inlineStr">
+      <c r="K237" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
@@ -11848,7 +11134,7 @@
         <v>280</v>
       </c>
       <c r="E238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F238" t="n">
         <v>50</v>
@@ -11871,10 +11157,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K238" t="n">
-        <v>2</v>
-      </c>
-      <c r="L238" t="inlineStr">
+      <c r="K238" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -11896,7 +11179,7 @@
         <v>1460</v>
       </c>
       <c r="E239" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F239" t="n">
         <v>360</v>
@@ -11919,10 +11202,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K239" t="n">
-        <v>3</v>
-      </c>
-      <c r="L239" t="inlineStr">
+      <c r="K239" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -11944,7 +11224,7 @@
         <v>1460</v>
       </c>
       <c r="E240" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F240" t="n">
         <v>360</v>
@@ -11967,10 +11247,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K240" t="n">
-        <v>3</v>
-      </c>
-      <c r="L240" t="inlineStr">
+      <c r="K240" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -11992,7 +11269,7 @@
         <v>1460</v>
       </c>
       <c r="E241" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F241" t="n">
         <v>360</v>
@@ -12015,10 +11292,7 @@
           <t>2628</t>
         </is>
       </c>
-      <c r="K241" t="n">
-        <v>3</v>
-      </c>
-      <c r="L241" t="inlineStr">
+      <c r="K241" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12040,7 +11314,7 @@
         <v>1460</v>
       </c>
       <c r="E242" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F242" t="n">
         <v>360</v>
@@ -12063,10 +11337,7 @@
           <t>2628</t>
         </is>
       </c>
-      <c r="K242" t="n">
-        <v>3</v>
-      </c>
-      <c r="L242" t="inlineStr">
+      <c r="K242" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12088,7 +11359,7 @@
         <v>1520</v>
       </c>
       <c r="E243" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F243" t="n">
         <v>250</v>
@@ -12111,10 +11382,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K243" t="n">
-        <v>28</v>
-      </c>
-      <c r="L243" t="inlineStr">
+      <c r="K243" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12159,10 +11427,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K244" t="n">
-        <v>1</v>
-      </c>
-      <c r="L244" t="inlineStr">
+      <c r="K244" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12207,10 +11472,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K245" t="n">
-        <v>1</v>
-      </c>
-      <c r="L245" t="inlineStr">
+      <c r="K245" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12232,7 +11494,7 @@
         <v>780</v>
       </c>
       <c r="E246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F246" t="n">
         <v>100</v>
@@ -12255,10 +11517,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K246" t="n">
-        <v>2</v>
-      </c>
-      <c r="L246" t="inlineStr">
+      <c r="K246" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12303,10 +11562,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K247" t="n">
-        <v>1</v>
-      </c>
-      <c r="L247" t="inlineStr">
+      <c r="K247" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12328,7 +11584,7 @@
         <v>790</v>
       </c>
       <c r="E248" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F248" t="n">
         <v>250</v>
@@ -12351,10 +11607,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K248" t="n">
-        <v>4</v>
-      </c>
-      <c r="L248" t="inlineStr">
+      <c r="K248" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12376,7 +11629,7 @@
         <v>1200</v>
       </c>
       <c r="E249" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F249" t="n">
         <v>150</v>
@@ -12399,10 +11652,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K249" t="n">
-        <v>13</v>
-      </c>
-      <c r="L249" t="inlineStr">
+      <c r="K249" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12424,7 +11674,7 @@
         <v>1010</v>
       </c>
       <c r="E250" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F250" t="n">
         <v>650</v>
@@ -12447,10 +11697,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K250" t="n">
-        <v>5</v>
-      </c>
-      <c r="L250" t="inlineStr">
+      <c r="K250" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12472,7 +11719,7 @@
         <v>1380</v>
       </c>
       <c r="E251" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F251" t="n">
         <v>72</v>
@@ -12495,10 +11742,7 @@
           <t>2624</t>
         </is>
       </c>
-      <c r="K251" t="n">
-        <v>25</v>
-      </c>
-      <c r="L251" t="inlineStr">
+      <c r="K251" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12520,7 +11764,7 @@
         <v>845</v>
       </c>
       <c r="E252" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F252" t="n">
         <v>200</v>
@@ -12543,10 +11787,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K252" t="n">
-        <v>4</v>
-      </c>
-      <c r="L252" t="inlineStr">
+      <c r="K252" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12591,10 +11832,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K253" t="n">
-        <v>1</v>
-      </c>
-      <c r="L253" t="inlineStr">
+      <c r="K253" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12639,10 +11877,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K254" t="n">
-        <v>1</v>
-      </c>
-      <c r="L254" t="inlineStr">
+      <c r="K254" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12664,7 +11899,7 @@
         <v>1200</v>
       </c>
       <c r="E255" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F255" t="n">
         <v>500</v>
@@ -12687,10 +11922,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K255" t="n">
-        <v>3</v>
-      </c>
-      <c r="L255" t="inlineStr">
+      <c r="K255" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12712,7 +11944,7 @@
         <v>1200</v>
       </c>
       <c r="E256" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F256" t="n">
         <v>500</v>
@@ -12735,10 +11967,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K256" t="n">
-        <v>3</v>
-      </c>
-      <c r="L256" t="inlineStr">
+      <c r="K256" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12760,7 +11989,7 @@
         <v>1460</v>
       </c>
       <c r="E257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F257" t="n">
         <v>360</v>
@@ -12783,10 +12012,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K257" t="n">
-        <v>2</v>
-      </c>
-      <c r="L257" t="inlineStr">
+      <c r="K257" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12808,7 +12034,7 @@
         <v>820</v>
       </c>
       <c r="E258" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F258" t="n">
         <v>230</v>
@@ -12831,10 +12057,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K258" t="n">
-        <v>18</v>
-      </c>
-      <c r="L258" t="inlineStr">
+      <c r="K258" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12879,10 +12102,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K259" t="n">
-        <v>1</v>
-      </c>
-      <c r="L259" t="inlineStr">
+      <c r="K259" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12927,10 +12147,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K260" t="n">
-        <v>1</v>
-      </c>
-      <c r="L260" t="inlineStr">
+      <c r="K260" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -12975,10 +12192,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K261" t="n">
-        <v>1</v>
-      </c>
-      <c r="L261" t="inlineStr">
+      <c r="K261" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
@@ -13000,7 +12214,7 @@
         <v>1270</v>
       </c>
       <c r="E262" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F262" t="n">
         <v>38</v>
@@ -13023,10 +12237,7 @@
           <t>2631</t>
         </is>
       </c>
-      <c r="K262" t="n">
-        <v>27</v>
-      </c>
-      <c r="L262" t="inlineStr">
+      <c r="K262" t="inlineStr">
         <is>
           <t>2625</t>
         </is>
@@ -13048,7 +12259,7 @@
         <v>1040</v>
       </c>
       <c r="E263" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F263" t="n">
         <v>650</v>
@@ -13071,10 +12282,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K263" t="n">
-        <v>3</v>
-      </c>
-      <c r="L263" t="inlineStr">
+      <c r="K263" t="inlineStr">
         <is>
           <t>2625</t>
         </is>
@@ -13096,7 +12304,7 @@
         <v>1210</v>
       </c>
       <c r="E264" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F264" t="n">
         <v>150</v>
@@ -13119,10 +12327,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K264" t="n">
-        <v>13</v>
-      </c>
-      <c r="L264" t="inlineStr">
+      <c r="K264" t="inlineStr">
         <is>
           <t>2625</t>
         </is>
@@ -13144,7 +12349,7 @@
         <v>1690</v>
       </c>
       <c r="E265" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F265" t="n">
         <v>55</v>
@@ -13167,10 +12372,7 @@
           <t>2630</t>
         </is>
       </c>
-      <c r="K265" t="n">
-        <v>15</v>
-      </c>
-      <c r="L265" t="inlineStr">
+      <c r="K265" t="inlineStr">
         <is>
           <t>2625</t>
         </is>
@@ -13192,7 +12394,7 @@
         <v>1360</v>
       </c>
       <c r="E266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F266" t="n">
         <v>400</v>
@@ -13215,10 +12417,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K266" t="n">
-        <v>2</v>
-      </c>
-      <c r="L266" t="inlineStr">
+      <c r="K266" t="inlineStr">
         <is>
           <t>2625</t>
         </is>
@@ -13240,7 +12439,7 @@
         <v>0</v>
       </c>
       <c r="E267" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F267" t="n">
         <v>400</v>
@@ -13263,10 +12462,7 @@
           <t>2625</t>
         </is>
       </c>
-      <c r="K267" t="n">
-        <v>4</v>
-      </c>
-      <c r="L267" t="inlineStr">
+      <c r="K267" t="inlineStr">
         <is>
           <t>2625</t>
         </is>
@@ -13288,7 +12484,7 @@
         <v>1450</v>
       </c>
       <c r="E268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F268" t="n">
         <v>2200</v>
@@ -13311,10 +12507,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K268" t="n">
-        <v>2</v>
-      </c>
-      <c r="L268" t="inlineStr">
+      <c r="K268" t="inlineStr">
         <is>
           <t>2625</t>
         </is>
@@ -13336,7 +12529,7 @@
         <v>950</v>
       </c>
       <c r="E269" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F269" t="n">
         <v>750</v>
@@ -13359,10 +12552,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K269" t="n">
-        <v>6</v>
-      </c>
-      <c r="L269" t="inlineStr">
+      <c r="K269" t="inlineStr">
         <is>
           <t>2625</t>
         </is>
@@ -13384,7 +12574,7 @@
         <v>1050</v>
       </c>
       <c r="E270" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F270" t="n">
         <v>200</v>
@@ -13407,10 +12597,7 @@
           <t>2629</t>
         </is>
       </c>
-      <c r="K270" t="n">
-        <v>3</v>
-      </c>
-      <c r="L270" t="inlineStr">
+      <c r="K270" t="inlineStr">
         <is>
           <t>2626</t>
         </is>
@@ -13432,7 +12619,7 @@
         <v>1170</v>
       </c>
       <c r="E271" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F271" t="n">
         <v>55</v>
@@ -13455,10 +12642,7 @@
           <t>2630</t>
         </is>
       </c>
-      <c r="K271" t="n">
-        <v>3</v>
-      </c>
-      <c r="L271" t="inlineStr">
+      <c r="K271" t="inlineStr">
         <is>
           <t>2626</t>
         </is>
@@ -13503,10 +12687,7 @@
           <t>2630</t>
         </is>
       </c>
-      <c r="K272" t="n">
-        <v>1</v>
-      </c>
-      <c r="L272" t="inlineStr">
+      <c r="K272" t="inlineStr">
         <is>
           <t>2626</t>
         </is>
@@ -13528,7 +12709,7 @@
         <v>1070</v>
       </c>
       <c r="E273" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F273" t="n">
         <v>350</v>
@@ -13551,10 +12732,7 @@
           <t>2630</t>
         </is>
       </c>
-      <c r="K273" t="n">
-        <v>9</v>
-      </c>
-      <c r="L273" t="inlineStr">
+      <c r="K273" t="inlineStr">
         <is>
           <t>2626</t>
         </is>
@@ -13576,7 +12754,7 @@
         <v>1200</v>
       </c>
       <c r="E274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F274" t="n">
         <v>500</v>
@@ -13599,10 +12777,7 @@
           <t>2630</t>
         </is>
       </c>
-      <c r="K274" t="n">
-        <v>2</v>
-      </c>
-      <c r="L274" t="inlineStr">
+      <c r="K274" t="inlineStr">
         <is>
           <t>2626</t>
         </is>
@@ -13647,10 +12822,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K275" t="n">
-        <v>1</v>
-      </c>
-      <c r="L275" t="inlineStr">
+      <c r="K275" t="inlineStr">
         <is>
           <t>2626</t>
         </is>
@@ -13672,7 +12844,7 @@
         <v>1160</v>
       </c>
       <c r="E276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F276" t="n">
         <v>600</v>
@@ -13695,10 +12867,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K276" t="n">
-        <v>2</v>
-      </c>
-      <c r="L276" t="inlineStr">
+      <c r="K276" t="inlineStr">
         <is>
           <t>2626</t>
         </is>
@@ -13720,7 +12889,7 @@
         <v>1040</v>
       </c>
       <c r="E277" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F277" t="n">
         <v>1200</v>
@@ -13743,10 +12912,7 @@
           <t>2628</t>
         </is>
       </c>
-      <c r="K277" t="n">
-        <v>4</v>
-      </c>
-      <c r="L277" t="inlineStr">
+      <c r="K277" t="inlineStr">
         <is>
           <t>2626</t>
         </is>
@@ -13768,7 +12934,7 @@
         <v>1460</v>
       </c>
       <c r="E278" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F278" t="n">
         <v>360</v>
@@ -13791,10 +12957,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K278" t="n">
-        <v>7</v>
-      </c>
-      <c r="L278" t="inlineStr">
+      <c r="K278" t="inlineStr">
         <is>
           <t>2626</t>
         </is>
@@ -13839,10 +13002,7 @@
           <t>2627</t>
         </is>
       </c>
-      <c r="K279" t="n">
-        <v>1</v>
-      </c>
-      <c r="L279" t="inlineStr">
+      <c r="K279" t="inlineStr">
         <is>
           <t>2626</t>
         </is>
@@ -13864,7 +13024,7 @@
         <v>760</v>
       </c>
       <c r="E280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F280" t="n">
         <v>150</v>
@@ -13887,10 +13047,7 @@
           <t>2628</t>
         </is>
       </c>
-      <c r="K280" t="n">
-        <v>2</v>
-      </c>
-      <c r="L280" t="inlineStr">
+      <c r="K280" t="inlineStr">
         <is>
           <t>2627</t>
         </is>
@@ -13912,7 +13069,7 @@
         <v>760</v>
       </c>
       <c r="E281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F281" t="n">
         <v>150</v>
@@ -13935,10 +13092,7 @@
           <t>2628</t>
         </is>
       </c>
-      <c r="K281" t="n">
-        <v>2</v>
-      </c>
-      <c r="L281" t="inlineStr">
+      <c r="K281" t="inlineStr">
         <is>
           <t>2627</t>
         </is>
@@ -13960,7 +13114,7 @@
         <v>1040</v>
       </c>
       <c r="E282" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F282" t="n">
         <v>160</v>
@@ -13983,10 +13137,7 @@
           <t>2628</t>
         </is>
       </c>
-      <c r="K282" t="n">
-        <v>3</v>
-      </c>
-      <c r="L282" t="inlineStr">
+      <c r="K282" t="inlineStr">
         <is>
           <t>2627</t>
         </is>
@@ -14008,7 +13159,7 @@
         <v>790</v>
       </c>
       <c r="E283" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F283" t="n">
         <v>250</v>
@@ -14031,10 +13182,7 @@
           <t>2631</t>
         </is>
       </c>
-      <c r="K283" t="n">
-        <v>4</v>
-      </c>
-      <c r="L283" t="inlineStr">
+      <c r="K283" t="inlineStr">
         <is>
           <t>2627</t>
         </is>
@@ -14056,7 +13204,7 @@
         <v>1670</v>
       </c>
       <c r="E284" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F284" t="n">
         <v>55</v>
@@ -14079,10 +13227,7 @@
           <t>2628</t>
         </is>
       </c>
-      <c r="K284" t="n">
-        <v>4</v>
-      </c>
-      <c r="L284" t="inlineStr">
+      <c r="K284" t="inlineStr">
         <is>
           <t>2627</t>
         </is>
@@ -14127,10 +13272,7 @@
           <t>2628</t>
         </is>
       </c>
-      <c r="K285" t="n">
-        <v>1</v>
-      </c>
-      <c r="L285" t="inlineStr">
+      <c r="K285" t="inlineStr">
         <is>
           <t>2627</t>
         </is>
@@ -14175,10 +13317,7 @@
           <t>2628</t>
         </is>
       </c>
-      <c r="K286" t="n">
-        <v>1</v>
-      </c>
-      <c r="L286" t="inlineStr">
+      <c r="K286" t="inlineStr">
         <is>
           <t>2627</t>
         </is>
@@ -14223,10 +13362,7 @@
           <t>2628</t>
         </is>
       </c>
-      <c r="K287" t="n">
-        <v>1</v>
-      </c>
-      <c r="L287" t="inlineStr">
+      <c r="K287" t="inlineStr">
         <is>
           <t>2627</t>
         </is>
@@ -14271,10 +13407,7 @@
           <t>2629</t>
         </is>
       </c>
-      <c r="K288" t="n">
-        <v>1</v>
-      </c>
-      <c r="L288" t="inlineStr">
+      <c r="K288" t="inlineStr">
         <is>
           <t>2627</t>
         </is>
@@ -14296,7 +13429,7 @@
         <v>1330</v>
       </c>
       <c r="E289" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F289" t="n">
         <v>400</v>
@@ -14319,10 +13452,7 @@
           <t>2626</t>
         </is>
       </c>
-      <c r="K289" t="n">
-        <v>5</v>
-      </c>
-      <c r="L289" t="inlineStr">
+      <c r="K289" t="inlineStr">
         <is>
           <t>2628</t>
         </is>
@@ -14344,7 +13474,7 @@
         <v>1170</v>
       </c>
       <c r="E290" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F290" t="n">
         <v>55</v>
@@ -14367,10 +13497,7 @@
           <t>2653</t>
         </is>
       </c>
-      <c r="K290" t="n">
-        <v>4</v>
-      </c>
-      <c r="L290" t="inlineStr">
+      <c r="K290" t="inlineStr">
         <is>
           <t>2628</t>
         </is>
@@ -14415,10 +13542,7 @@
           <t>2629</t>
         </is>
       </c>
-      <c r="K291" t="n">
-        <v>1</v>
-      </c>
-      <c r="L291" t="inlineStr">
+      <c r="K291" t="inlineStr">
         <is>
           <t>2628</t>
         </is>
@@ -14463,10 +13587,7 @@
           <t>2629</t>
         </is>
       </c>
-      <c r="K292" t="n">
-        <v>1</v>
-      </c>
-      <c r="L292" t="inlineStr">
+      <c r="K292" t="inlineStr">
         <is>
           <t>2628</t>
         </is>
@@ -14511,10 +13632,7 @@
           <t>2629</t>
         </is>
       </c>
-      <c r="K293" t="n">
-        <v>1</v>
-      </c>
-      <c r="L293" t="inlineStr">
+      <c r="K293" t="inlineStr">
         <is>
           <t>2628</t>
         </is>
@@ -14536,7 +13654,7 @@
         <v>0</v>
       </c>
       <c r="E294" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F294" t="n">
         <v>50</v>
@@ -14559,10 +13677,7 @@
           <t>2620</t>
         </is>
       </c>
-      <c r="K294" t="n">
-        <v>2</v>
-      </c>
-      <c r="L294" t="inlineStr">
+      <c r="K294" t="inlineStr">
         <is>
           <t>2629</t>
         </is>
@@ -14584,7 +13699,7 @@
         <v>1400</v>
       </c>
       <c r="E295" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F295" t="n">
         <v>1200</v>
@@ -14607,10 +13722,7 @@
           <t>2636</t>
         </is>
       </c>
-      <c r="K295" t="n">
-        <v>6</v>
-      </c>
-      <c r="L295" t="inlineStr">
+      <c r="K295" t="inlineStr">
         <is>
           <t>2630</t>
         </is>
@@ -14632,7 +13744,7 @@
         <v>800</v>
       </c>
       <c r="E296" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F296" t="n">
         <v>500</v>
@@ -14655,10 +13767,7 @@
           <t>2636</t>
         </is>
       </c>
-      <c r="K296" t="n">
-        <v>7</v>
-      </c>
-      <c r="L296" t="inlineStr">
+      <c r="K296" t="inlineStr">
         <is>
           <t>2630</t>
         </is>
@@ -14703,10 +13812,7 @@
           <t>2631</t>
         </is>
       </c>
-      <c r="K297" t="n">
-        <v>1</v>
-      </c>
-      <c r="L297" t="inlineStr">
+      <c r="K297" t="inlineStr">
         <is>
           <t>2630</t>
         </is>
@@ -14751,10 +13857,7 @@
           <t>2635</t>
         </is>
       </c>
-      <c r="K298" t="n">
-        <v>1</v>
-      </c>
-      <c r="L298" t="inlineStr">
+      <c r="K298" t="inlineStr">
         <is>
           <t>2630</t>
         </is>
@@ -14799,10 +13902,7 @@
           <t>2633</t>
         </is>
       </c>
-      <c r="K299" t="n">
-        <v>1</v>
-      </c>
-      <c r="L299" t="inlineStr">
+      <c r="K299" t="inlineStr">
         <is>
           <t>2630</t>
         </is>
@@ -14824,7 +13924,7 @@
         <v>0</v>
       </c>
       <c r="E300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F300" t="n">
         <v>400</v>
@@ -14847,10 +13947,7 @@
           <t>2631</t>
         </is>
       </c>
-      <c r="K300" t="n">
-        <v>2</v>
-      </c>
-      <c r="L300" t="inlineStr">
+      <c r="K300" t="inlineStr">
         <is>
           <t>2630</t>
         </is>
@@ -14872,7 +13969,7 @@
         <v>0</v>
       </c>
       <c r="E301" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F301" t="n">
         <v>360</v>
@@ -14895,10 +13992,7 @@
           <t>2634</t>
         </is>
       </c>
-      <c r="K301" t="n">
-        <v>10</v>
-      </c>
-      <c r="L301" t="inlineStr">
+      <c r="K301" t="inlineStr">
         <is>
           <t>2630</t>
         </is>
@@ -14920,7 +14014,7 @@
         <v>1530</v>
       </c>
       <c r="E302" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F302" t="n">
         <v>750</v>
@@ -14943,10 +14037,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K302" t="n">
-        <v>15</v>
-      </c>
-      <c r="L302" t="inlineStr">
+      <c r="K302" t="inlineStr">
         <is>
           <t>2631</t>
         </is>
@@ -14968,7 +14059,7 @@
         <v>1530</v>
       </c>
       <c r="E303" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F303" t="n">
         <v>750</v>
@@ -14991,10 +14082,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K303" t="n">
-        <v>12</v>
-      </c>
-      <c r="L303" t="inlineStr">
+      <c r="K303" t="inlineStr">
         <is>
           <t>2631</t>
         </is>
@@ -15016,7 +14104,7 @@
         <v>1125</v>
       </c>
       <c r="E304" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F304" t="n">
         <v>150</v>
@@ -15039,10 +14127,7 @@
           <t>2635</t>
         </is>
       </c>
-      <c r="K304" t="n">
-        <v>14</v>
-      </c>
-      <c r="L304" t="inlineStr">
+      <c r="K304" t="inlineStr">
         <is>
           <t>2631</t>
         </is>
@@ -15064,7 +14149,7 @@
         <v>1440</v>
       </c>
       <c r="E305" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F305" t="n">
         <v>360</v>
@@ -15087,10 +14172,7 @@
           <t>2636</t>
         </is>
       </c>
-      <c r="K305" t="n">
-        <v>19</v>
-      </c>
-      <c r="L305" t="inlineStr">
+      <c r="K305" t="inlineStr">
         <is>
           <t>2632</t>
         </is>
@@ -15135,10 +14217,7 @@
           <t>2639</t>
         </is>
       </c>
-      <c r="K306" t="n">
-        <v>1</v>
-      </c>
-      <c r="L306" t="inlineStr">
+      <c r="K306" t="inlineStr">
         <is>
           <t>2633</t>
         </is>
@@ -15160,7 +14239,7 @@
         <v>360</v>
       </c>
       <c r="E307" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F307" t="n">
         <v>200</v>
@@ -15183,10 +14262,7 @@
           <t>2701</t>
         </is>
       </c>
-      <c r="K307" t="n">
-        <v>2</v>
-      </c>
-      <c r="L307" t="inlineStr">
+      <c r="K307" t="inlineStr">
         <is>
           <t>2645</t>
         </is>
